--- a/Testen/Test08_EqualMachineTime.xlsx
+++ b/Testen/Test08_EqualMachineTime.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2810a0d4408f349/Documenten/GitHub/OR5/Testen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76A19DA0-E144-45C9-A93E-6BFCCADDED18}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A5F62C2-6ADB-43C1-A31B-16BC1CDA8F87}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
@@ -460,16 +460,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.54296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.36328125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -486,7 +486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>16</v>
       </c>
@@ -520,7 +520,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
@@ -546,13 +546,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.81640625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -560,7 +560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -568,7 +568,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15.5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -584,14 +584,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -602,7 +602,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -624,7 +624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -635,7 +635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -646,7 +646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -657,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -668,7 +668,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
@@ -679,7 +679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -690,7 +690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
@@ -708,6 +708,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010013B620F01982514694878B55267266B0" ma:contentTypeVersion="86" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="74461f5d53f32db2b022b75481ad65d4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xmlns:ns3="c6fe3531-949f-4c96-ac1d-b793c48e3f25" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f35a72610264df809623b370168ef8a" ns2:_="" ns3:_="">
     <xsd:import namespace="882bdec5-c3ce-4705-9a84-58ed8ad203ea"/>
@@ -934,24 +951,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="882bdec5-c3ce-4705-9a84-58ed8ad203ea" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F853DD-D83E-469C-9E1E-915877D838F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A6ABA0-C4D6-4A20-974A-2B1B1E891161}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="882bdec5-c3ce-4705-9a84-58ed8ad203ea"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DCD283C-A444-4931-8008-3456731CDA06}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -968,22 +986,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58A6ABA0-C4D6-4A20-974A-2B1B1E891161}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="882bdec5-c3ce-4705-9a84-58ed8ad203ea"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F853DD-D83E-469C-9E1E-915877D838F7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>